--- a/data/2025/15-covasna/63394-sfantu-gheorghe/budget_file.xlsx
+++ b/data/2025/15-covasna/63394-sfantu-gheorghe/budget_file.xlsx
@@ -7731,30 +7731,37 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" t="inlineStr">
+      <c r="A236" s="3" t="inlineStr">
         <is>
           <t>51.02</t>
         </is>
       </c>
-      <c r="C236" t="inlineStr">
+      <c r="B236" s="3" t="n"/>
+      <c r="C236" s="3" t="inlineStr">
         <is>
           <t>Autoritati publice si actiuni externe(cod 51.02.01)</t>
         </is>
       </c>
-      <c r="E236" t="n">
+      <c r="D236" s="3" t="n"/>
+      <c r="E236" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="F236" t="inlineStr">
+      <c r="F236" s="3" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G236" s="2" t="n">
+      <c r="G236" s="4" t="n">
         <v>25001800</v>
       </c>
-      <c r="H236" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="H236" s="3" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I236" s="3" t="inlineStr">
+        <is>
+          <t>51.02 total_2026: parent 25.001.800,00 != sum(children) 886.800,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -11859,30 +11866,37 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" t="inlineStr">
+      <c r="A364" s="3" t="inlineStr">
         <is>
           <t>65.02</t>
         </is>
       </c>
-      <c r="C364" t="inlineStr">
+      <c r="B364" s="3" t="n"/>
+      <c r="C364" s="3" t="inlineStr">
         <is>
           <t>Invatamant (cod 65.02.03 la 65.02.05+65.02.07+65.02.11+65.02.12+65.02.50)</t>
         </is>
       </c>
-      <c r="E364" t="n">
+      <c r="D364" s="3" t="n"/>
+      <c r="E364" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="F364" t="inlineStr">
+      <c r="F364" s="3" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G364" s="2" t="n">
+      <c r="G364" s="4" t="n">
         <v>72351120</v>
       </c>
-      <c r="H364" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="H364" s="3" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I364" s="3" t="inlineStr">
+        <is>
+          <t>65.02 total_2026: parent 72.351.120,00 != sum(children) 11.011.650,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -23055,30 +23069,37 @@
       </c>
     </row>
     <row r="713">
-      <c r="A713" t="inlineStr">
+      <c r="A713" s="3" t="inlineStr">
         <is>
           <t>74.02</t>
         </is>
       </c>
-      <c r="C713" t="inlineStr">
+      <c r="B713" s="3" t="n"/>
+      <c r="C713" s="3" t="inlineStr">
         <is>
           <t>Protectia mediului (cod 74.02.03+74.02.05+74.02.06+74.02.50)</t>
         </is>
       </c>
-      <c r="E713" t="n">
+      <c r="D713" s="3" t="n"/>
+      <c r="E713" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="F713" t="inlineStr">
+      <c r="F713" s="3" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G713" s="2" t="n">
+      <c r="G713" s="4" t="n">
         <v>16868830</v>
       </c>
-      <c r="H713" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="H713" s="3" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I713" s="3" t="inlineStr">
+        <is>
+          <t>74.02 total_2026: parent 16.868.830,00 != sum(children) 2.876.650,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -25350,39 +25371,39 @@
       </c>
     </row>
     <row r="783">
-      <c r="A783" s="5" t="inlineStr">
+      <c r="A783" s="3" t="inlineStr">
         <is>
           <t>84.02</t>
         </is>
       </c>
-      <c r="B783" s="5" t="n"/>
-      <c r="C783" s="5" t="inlineStr">
+      <c r="B783" s="3" t="n"/>
+      <c r="C783" s="3" t="inlineStr">
         <is>
           <t>ra..+.+.+ . .50)</t>
         </is>
       </c>
-      <c r="D783" s="5" t="n">
+      <c r="D783" s="3" t="n">
         <v>10227</v>
       </c>
-      <c r="E783" s="5" t="n">
+      <c r="E783" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="F783" s="5" t="inlineStr">
+      <c r="F783" s="3" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G783" s="6" t="n">
+      <c r="G783" s="4" t="n">
         <v>72742050</v>
       </c>
-      <c r="H783" s="5" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="I783" s="5" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (14%): 'ra..+.+.+ . .50)' vs 'Transporturi'</t>
+      <c r="H783" s="3" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I783" s="3" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (14%): 'ra..+.+.+ . .50)' vs 'Transporturi'; 84.02 total_2026: parent 72.742.050,00 != sum(children) 11.309.050,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -38987,40 +39008,39 @@
       </c>
     </row>
     <row r="1200">
-      <c r="A1200" t="inlineStr">
+      <c r="A1200" s="3" t="inlineStr">
         <is>
           <t>10.02.06</t>
         </is>
       </c>
-      <c r="B1200" t="inlineStr">
+      <c r="B1200" s="3" t="inlineStr">
         <is>
           <t>66.02</t>
         </is>
       </c>
-      <c r="C1200" t="inlineStr">
+      <c r="C1200" s="3" t="inlineStr">
         <is>
           <t>Vouchere de vacanta</t>
         </is>
       </c>
-      <c r="E1200" t="n">
+      <c r="D1200" s="3" t="n"/>
+      <c r="E1200" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="F1200" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G1200" s="2" t="n">
-        <v>33000</v>
-      </c>
-      <c r="H1200" t="inlineStr">
-        <is>
-          <t>llm:gemini-3.6-flash</t>
-        </is>
-      </c>
-      <c r="I1200" t="inlineStr">
-        <is>
-          <t>cell re-read from image (unverified transcription)</t>
+      <c r="F1200" s="3" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G1200" s="4" t="n"/>
+      <c r="H1200" s="3" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I1200" s="3" t="inlineStr">
+        <is>
+          <t>unparseable cell '33.000,00 103.500,00' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -39590,35 +39610,35 @@
       </c>
     </row>
     <row r="1218">
-      <c r="A1218" t="inlineStr">
+      <c r="A1218" s="3" t="inlineStr">
         <is>
           <t>66.02.06</t>
         </is>
       </c>
-      <c r="C1218" t="inlineStr">
+      <c r="B1218" s="3" t="n"/>
+      <c r="C1218" s="3" t="inlineStr">
         <is>
           <t>Servicii medicale in unitati sanitare cu paturi(cod 66.02.06.01+66.02.06.03)</t>
         </is>
       </c>
-      <c r="E1218" t="n">
+      <c r="D1218" s="3" t="n"/>
+      <c r="E1218" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="F1218" t="inlineStr">
+      <c r="F1218" s="3" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G1218" s="2" t="n">
-        <v>999840</v>
-      </c>
-      <c r="H1218" t="inlineStr">
-        <is>
-          <t>llm:gemini-3.6-flash</t>
-        </is>
-      </c>
-      <c r="I1218" t="inlineStr">
-        <is>
-          <t>cell re-read from image (unverified transcription)</t>
+      <c r="G1218" s="4" t="n"/>
+      <c r="H1218" s="3" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I1218" s="3" t="inlineStr">
+        <is>
+          <t>unparseable cell "99'048.0" in column total_2026; 66.02.06 total_2026: parent 0,00 != sum(children) 99.048,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -39642,11 +39662,11 @@
         </is>
       </c>
       <c r="G1219" s="2" t="n">
-        <v>999840</v>
+        <v>99048</v>
       </c>
       <c r="H1219" t="inlineStr">
         <is>
-          <t>llm:gemini-3.6-flash</t>
+          <t>ocr</t>
         </is>
       </c>
     </row>
@@ -46090,40 +46110,39 @@
       </c>
     </row>
     <row r="1424">
-      <c r="A1424" t="inlineStr">
+      <c r="A1424" s="3" t="inlineStr">
         <is>
           <t>10.01</t>
         </is>
       </c>
-      <c r="B1424" t="inlineStr">
+      <c r="B1424" s="3" t="inlineStr">
         <is>
           <t>83.02</t>
         </is>
       </c>
-      <c r="C1424" t="inlineStr">
+      <c r="C1424" s="3" t="inlineStr">
         <is>
           <t>Cheltuieli salariale in bani</t>
         </is>
       </c>
-      <c r="E1424" t="n">
+      <c r="D1424" s="3" t="n"/>
+      <c r="E1424" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="F1424" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G1424" s="2" t="n">
-        <v>143900</v>
-      </c>
-      <c r="H1424" t="inlineStr">
-        <is>
-          <t>llm:gemini-3.6-flash</t>
-        </is>
-      </c>
-      <c r="I1424" t="inlineStr">
-        <is>
-          <t>cell re-read from image (unverified transcription)</t>
+      <c r="F1424" s="3" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G1424" s="4" t="n"/>
+      <c r="H1424" s="3" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I1424" s="3" t="inlineStr">
+        <is>
+          <t>unparseable cell '143.900,00 135.700,00' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -46677,30 +46696,37 @@
       </c>
     </row>
     <row r="1442">
-      <c r="A1442" t="inlineStr">
+      <c r="A1442" s="3" t="inlineStr">
         <is>
           <t>84.02</t>
         </is>
       </c>
-      <c r="C1442" t="inlineStr">
+      <c r="B1442" s="3" t="n"/>
+      <c r="C1442" s="3" t="inlineStr">
         <is>
           <t>Transporturi (cod 84.02.03+84.02.04+84.02.06+84.02.50)</t>
         </is>
       </c>
-      <c r="E1442" t="n">
+      <c r="D1442" s="3" t="n"/>
+      <c r="E1442" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="F1442" t="inlineStr">
+      <c r="F1442" s="3" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G1442" s="2" t="n">
+      <c r="G1442" s="4" t="n">
         <v>10330600</v>
       </c>
-      <c r="H1442" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="H1442" s="3" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I1442" s="3" t="inlineStr">
+        <is>
+          <t>84.02 total_2026: parent 10.330.600,00 != sum(children) 3.630.600,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -56822,7 +56848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F168"/>
+  <dimension ref="A1:F154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -56868,157 +56894,132 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>51.02</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>02</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 51.02 total_2026: sum now consistent — applied</t>
+          <t>code 02 (expense_economic) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>61.02</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>02</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 61.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>code 02 (expense_economic) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>65.02</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>02</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>LLM re-read 9 rows for 65.02 total_2026: sum now consistent — applied</t>
+          <t>code 02 (expense_economic) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>67.02</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>02</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 67.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>code 02 (expense_economic) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>71.01</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>02</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 71.01 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>code 02 (expense_economic) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -57027,191 +57028,161 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>70.02.03</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>35.02.01</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 70.02.03 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>name mismatch vs nomenclator (32%): 'Vvniie   li nd  s  i e  .02)' vs 'Venituri din amenzi si alte sanctiuni ap'</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>70.02.05</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>02</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 70.02.05 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>code 02 (expense_economic) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>74.02</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>02</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 74.02 total_2026: sum now consistent — applied</t>
+          <t>code 02 (expense_economic) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>80.02</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>02</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 80.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>code 02 (expense_economic) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>84.02</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>02</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 84.02 total_2026: sum now consistent — applied</t>
+          <t>code 02 (expense_economic) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>67.02</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>02</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 67.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>code 02 (expense_economic) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>49.02</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -57221,27 +57192,27 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 10 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>49.02 total_2026: parent 382.242.070,00 != sum(children) 44.321.140,00 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>10.03</t>
+          <t>51.02</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -57251,87 +57222,77 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 10.03 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>51.02 total_2026: parent 25.001.800,00 != sum(children) 886.800,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>66.02.06</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>85</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 66.02.06 total_2026: sum now consistent — applied</t>
+          <t>name mismatch vs nomenclator (27%): 'TITLL    I I      ENT' vs 'Titlul XXII Plăţi efectuate în anii prec'</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>84.02</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>85.01.01</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 84.02 total_2026: sum now consistent — applied</t>
+          <t>name mismatch vs nomenclator (28%): 'Pletl n  t  s   e    rt e  e cal' vs 'Plăţi efectuate în anii precedenţi şi re'</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>68.02</t>
+          <t>61.02</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -57341,27 +57302,27 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>LLM re-read 6 rows for 68.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>61.02 total_2026: parent 4.899.410,00 != sum(children) 291.010,00 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>61.02</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -57371,74 +57332,99 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>LLM re-read 5 rows for 70.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>61.02 total_2026: parent 4.899.410,00 != sum(children) 166.010,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>9</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>65.02</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>total_2026</t>
+        </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>unparseable-cell pass p27: 1 cells recovered</t>
+          <t>65.02 total_2026: parent 72.351.120,00 != sum(children) 11.011.650,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>11</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>unparseable-cell pass p28: 1 cells recovered</t>
+          <t>name mismatch vs nomenclator (24%): 'TITL    I I      ENT' vs 'Titlul XXII Plăţi efectuate în anii prec'</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>32</v>
+        <v>12</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>67.02</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>total_2026</t>
+        </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>unparseable-cell pass p32: 1 cells recovered</t>
+          <t>67.02 total_2026: parent 76.828.330,00 != sum(children) 36.688.060,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>V1_code</t>
+          <t>V4_hierarchy</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -57447,73 +57433,78 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>67.02</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>code 02 (expense_economic) not in nomenclator</t>
+          <t>67.02 total_2026: parent 76.828.330,00 != sum(children) 1.688.060,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>85</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>code 02 (expense_economic) not in nomenclator</t>
+          <t>name mismatch vs nomenclator (26%): 'TITLE    I       IENT' vs 'Titlul XXII Plăţi efectuate în anii prec'</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>67.02.05.03</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>code 02 (expense_economic) not in nomenclator</t>
+          <t>name mismatch vs nomenclator (40%): 'lnuee e e se  e ze dn n i deent' vs 'Intretinere gradini publice, parcuri, zo'</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>V1_code</t>
+          <t>V4_hierarchy</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -57522,98 +57513,108 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>68.02</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>code 02 (expense_economic) not in nomenclator</t>
+          <t>68.02 total_2026: parent 47.820.180,00 != sum(children) 4.119.900,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>58.01</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>code 02 (expense_economic) not in nomenclator</t>
+          <t>name mismatch vs nomenclator (25%): 'Pro l  g  (       .)' vs 'Programe din Fondul European de Dezvolta'</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>35.02.01</t>
+          <t>71.01</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (32%): 'Vvniie   li nd  s  i e  .02)' vs 'Venituri din amenzi si alte sanctiuni ap'</t>
+          <t>71.01 total_2026: parent 11.457.420,00 != sum(children) 11.498.230,00 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>85.01.01</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>code 02 (expense_economic) not in nomenclator</t>
+          <t>name mismatch vs nomenclator (24%): 'Plal     s   e   s r e  e ocal' vs 'Plăţi efectuate în anii precedenţi şi re'</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>V1_code</t>
+          <t>V4_hierarchy</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -57622,48 +57623,53 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>70.02.03</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>code 02 (expense_economic) not in nomenclator</t>
+          <t>70.02.03 total_2026: parent 14.033.930,00 != sum(children) 13.583.930,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>70.02.05</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>code 02 (expense_economic) not in nomenclator</t>
+          <t>name mismatch vs nomenclator (11%): 'A1ilm.+       .0)' vs 'Alimentare cu apa si amenajari hidrotehn'</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>V1_code</t>
+          <t>V4_hierarchy</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -57672,23 +57678,28 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>70.02.05</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>code 02 (expense_economic) not in nomenclator</t>
+          <t>70.02.05 total_2026: parent 3.870.000,00 != sum(children) 10.000,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>V1_code</t>
+          <t>V4_hierarchy</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -57697,16 +57708,21 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>74.02</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>code 02 (expense_economic) not in nomenclator</t>
+          <t>74.02 total_2026: parent 16.868.830,00 != sum(children) 2.876.650,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -57722,11 +57738,11 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>49.02</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -57736,32 +57752,37 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>49.02 total_2026: parent 382.242.070,00 != sum(children) 44.321.140,00 (3 children)</t>
+          <t>80.02 total_2026: parent 2.906.730,00 != sum(children) 145.600,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>80.02</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (27%): 'TITLL    I I      ENT' vs 'Titlul XXII Plăţi efectuate în anii prec'</t>
+          <t>80.02 total_2026: parent 2.906.730,00 != sum(children) 145.600,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -57777,16 +57798,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>85.01.01</t>
+          <t>84.02</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): 'Pletl n  t  s   e    rt e  e cal' vs 'Plăţi efectuate în anii precedenţi şi re'</t>
+          <t>name mismatch vs nomenclator (14%): 'ra..+.+.+ . .50)' vs 'Transporturi'</t>
         </is>
       </c>
     </row>
@@ -57802,11 +57823,11 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>61.02</t>
+          <t>84.02</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -57816,14 +57837,14 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.02 total_2026: parent 4.899.410,00 != sum(children) 291.010,00 (3 children)</t>
+          <t>84.02 total_2026: parent 72.742.050,00 != sum(children) 11.309.050,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
+          <t>V1_code</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -57832,53 +57853,48 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>61.02</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>02</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.02 total_2026: parent 4.899.410,00 != sum(children) 166.010,00 (1 children)</t>
+          <t>code 02 (expense_economic) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>02</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (24%): 'TITL    I I      ENT' vs 'Titlul XXII Plăţi efectuate în anii prec'</t>
+          <t>code 02 (expense_economic) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
+          <t>V1_code</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -57887,28 +57903,23 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>67.02</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>02</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>67.02 total_2026: parent 76.828.330,00 != sum(children) 36.688.060,00 (2 children)</t>
+          <t>code 02 (expense_economic) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
+          <t>V1_code</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -57917,46 +57928,41 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>67.02</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>02</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>67.02 total_2026: parent 76.828.330,00 != sum(children) 1.688.060,00 (2 children)</t>
+          <t>code 02 (expense_economic) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>02</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (26%): 'TITLE    I       IENT' vs 'Titlul XXII Plăţi efectuate în anii prec'</t>
+          <t>code 02 (expense_economic) not in nomenclator</t>
         </is>
       </c>
     </row>
@@ -57972,23 +57978,23 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>67.02.05.03</t>
+          <t>35.02.01</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (40%): 'lnuee e e se  e ze dn n i deent' vs 'Intretinere gradini publice, parcuri, zo'</t>
+          <t>name mismatch vs nomenclator (18%): 'Ven    ud    s   .02)' vs 'Venituri din amenzi si alte sanctiuni ap'</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
+          <t>V1_code</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -57997,53 +58003,48 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>68.02</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>02</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>68.02 total_2026: parent 47.820.180,00 != sum(children) 4.119.900,00 (2 children)</t>
+          <t>code 02 (expense_economic) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>58.01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (25%): 'Pro l  g  (       .)' vs 'Programe din Fondul European de Dezvolta'</t>
+          <t>code 02 (expense_economic) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
+          <t>V1_code</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -58052,21 +58053,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>71.01</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>02</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>71.01 total_2026: parent 11.457.420,00 != sum(children) 11.498.230,00 (3 children)</t>
+          <t>code 02 (expense_economic) not in nomenclator</t>
         </is>
       </c>
     </row>
@@ -58082,16 +58078,16 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>85.01.01</t>
+          <t>42.02.66</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (24%): 'Plal     s   e   s r e  e ocal' vs 'Plăţi efectuate în anii precedenţi şi re'</t>
+          <t>name mismatch vs nomenclator (33%): 'Ssubtd t d  d  o duort de  de c d ica' vs 'Subvenţii din bugetul de stat alocate co'</t>
         </is>
       </c>
     </row>
@@ -58107,11 +58103,11 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>70.02.03</t>
+          <t>49.02</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -58121,7 +58117,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>70.02.03 total_2026: parent 14.033.930,00 != sum(children) 13.583.930,00 (2 children)</t>
+          <t>49.02 total_2026: parent 177.769.320,00 != sum(children) 3.630.600,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -58137,76 +58133,66 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>70.02.05</t>
+          <t>85.01</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (11%): 'A1ilm.+       .0)' vs 'Alimentare cu apa si amenajari hidrotehn'</t>
+          <t>name mismatch vs nomenclator (28%): 'PLAE     I P   NT' vs 'Plăţi efectuate în anii precedenţi şi re'</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>70.02.05</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>85.01.01</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>70.02.05 total_2026: parent 3.870.000,00 != sum(children) 10.000,00 (2 children)</t>
+          <t>name mismatch vs nomenclator (32%): 'Plal n a t  es   e    r e e e ocal' vs 'Plăţi efectuate în anii precedenţi şi re'</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>80.02</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>80.02 total_2026: parent 2.906.730,00 != sum(children) 145.600,00 (2 children)</t>
+          <t>duplicate of p21 with different values</t>
         </is>
       </c>
     </row>
@@ -58216,27 +58202,22 @@
           <t>V4_hierarchy</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>info</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>80.02</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>80.02 total_2026: parent 2.906.730,00 != sum(children) 145.600,00 (1 children)</t>
+          <t>rând absent, derivat aritmetic din formula părintelui 63.02</t>
         </is>
       </c>
     </row>
@@ -58252,23 +58233,23 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>84.02</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (14%): 'ra..+.+.+ . .50)' vs 'Transporturi'</t>
+          <t>name mismatch vs nomenclator (32%): '(rând derivat din formula tipărită)' vs 'Cultura, recreere si religie'</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>V1_code</t>
+          <t>V4_hierarchy</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -58277,23 +58258,28 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>67.02</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>code 02 (expense_economic) not in nomenclator</t>
+          <t>67.02 total_2026: parent 32.425.370,00 != sum(children) 76.828.330,00 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>V1_code</t>
+          <t>V4_hierarchy</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -58302,23 +58288,28 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>code 02 (expense_economic) not in nomenclator</t>
+          <t>10 total_2026: parent 4.729.000,00 != sum(children) 4.625.500,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>V1_code</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -58327,23 +58318,23 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>20</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>02</t>
+        <v>27</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>code 02 (expense_economic) not in nomenclator</t>
+          <t>unparseable cell '33.000,00 103.500,00' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>V1_code</t>
+          <t>V4_hierarchy</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -58352,23 +58343,28 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>10.03</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>code 02 (expense_economic) not in nomenclator</t>
+          <t>10.03 total_2026: parent 0,00 != sum(children) 103.500,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>V1_code</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -58377,73 +58373,78 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>20</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>02</t>
+        <v>28</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>code 02 (expense_economic) not in nomenclator</t>
+          <t>unparseable cell "99'048.0" in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>35.02.01</t>
+          <t>66.02.06</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (18%): 'Ven    ud    s   .02)' vs 'Venituri din amenzi si alte sanctiuni ap'</t>
+          <t>66.02.06 total_2026: parent 0,00 != sum(children) 99.048,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>85.01.01</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>code 02 (expense_economic) not in nomenclator</t>
+          <t>name mismatch vs nomenclator (27%): 'Pla n a t  as  n         ocal' vs 'Plăţi efectuate în anii precedenţi şi re'</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>V1_code</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -58452,23 +58453,23 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>21</v>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>02</t>
+        <v>32</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>code 02 (expense_economic) not in nomenclator</t>
+          <t>unparseable cell '143.900,00 135.700,00' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>V1_code</t>
+          <t>V4_hierarchy</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -58477,48 +58478,53 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>84.02</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>code 02 (expense_economic) not in nomenclator</t>
+          <t>84.02 total_2026: parent 10.330.600,00 != sum(children) 3.630.600,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>42.02.66</t>
+          <t>02</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (33%): 'Ssubtd t d  d  o duort de  de c d ica' vs 'Subvenţii din bugetul de stat alocate co'</t>
+          <t>code 02 (expense_economic) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
+          <t>V1_code</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -58527,296 +58533,266 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>49.02</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>02</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>49.02 total_2026: parent 177.769.320,00 != sum(children) 3.630.600,00 (2 children)</t>
+          <t>code 02 (expense_economic) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>85.01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): 'PLAE     I P   NT' vs 'Plăţi efectuate în anii precedenţi şi re'</t>
+          <t>code 02 (expense_economic) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>85.01.01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (32%): 'Plal n a t  es   e    r e e e ocal' vs 'Plăţi efectuate în anii precedenţi şi re'</t>
+          <t>code 02 (expense_economic) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>duplicate of p21 with different values</t>
+          <t>code 02 (expense_economic) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>67.02</t>
+          <t>02</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>rând absent, derivat aritmetic din formula părintelui 63.02</t>
+          <t>duplicate of p2 with different values</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>67.02</t>
+          <t>02</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (32%): '(rând derivat din formula tipărită)' vs 'Cultura, recreere si religie'</t>
+          <t>code 02 (expense_economic) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>67.02</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>02</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>67.02 total_2026: parent 32.425.370,00 != sum(children) 76.828.330,00 (3 children)</t>
+          <t>duplicate of p2 with different values</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B70" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>42.02</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>10 total_2026: parent 4.729.000,00 != sum(children) 4.625.500,00 (2 children)</t>
+          <t>duplicate of p2 with different values</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>10.02.06</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>02</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>code 02 (expense_economic) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B72" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>10.03</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>02</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>10.03 total_2026: parent 0,00 != sum(children) 103.500,00 (1 children)</t>
+          <t>duplicate of p2 with different values</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>66.02.06</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>43.02</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
@@ -58832,178 +58808,173 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>85.01.01</t>
+          <t>45.02.48</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (27%): 'Pla n a t  as  n         ocal' vs 'Plăţi efectuate în anii precedenţi şi re'</t>
+          <t>name mismatch vs nomenclator (19%): 'Frn  -    (     1a 45.02.48.03)' vs 'Fondul European de Dezvoltare Regională '</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>10.01</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>49.02</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B76" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>code 02 (expense_economic) not in nomenclator</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B77" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>51</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>code 02 (expense_economic) not in nomenclator</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B78" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>85.01</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>code 02 (expense_economic) not in nomenclator</t>
+          <t>name mismatch vs nomenclator (29%): 'PLA     I S   NT' vs 'Plăţi efectuate în anii precedenţi şi re'</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B79" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>50.02</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>code 02 (expense_economic) not in nomenclator</t>
+          <t>duplicate of p6 with different values</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B80" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>info</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>56.02</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>code 02 (expense_economic) not in nomenclator</t>
+          <t>rând absent, derivat aritmetic din formula părintelui 50.02</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -59012,41 +58983,41 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>56.02</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>duplicate of p2 with different values</t>
+          <t>name mismatch vs nomenclator (36%): '(rând derivat din formula tipărită)' vs 'Transferuri cu caracter general intre di'</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B82" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>51.02</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>code 02 (expense_economic) not in nomenclator</t>
+          <t>duplicate of p6 with different values</t>
         </is>
       </c>
     </row>
@@ -59062,16 +59033,16 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>51.02.01</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>duplicate of p2 with different values</t>
+          <t>duplicate of p7 with different values</t>
         </is>
       </c>
     </row>
@@ -59087,73 +59058,73 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>42.02</t>
+          <t>51.02.01.03</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>duplicate of p2 with different values</t>
+          <t>duplicate of p7 with different values</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B85" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>code 02 (expense_economic) not in nomenclator</t>
+          <t>duplicate of p8 with different values</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V4_hierarchy</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>60.02</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>duplicate of p2 with different values</t>
+          <t>rând absent, derivat aritmetic din formula părintelui 59.02</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -59162,23 +59133,23 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>43.02</t>
+          <t>60.02</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>name mismatch vs nomenclator (24%): '(rând derivat din formula tipărită)' vs 'Aparare'</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -59187,48 +59158,48 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>45.02.48</t>
+          <t>61.02</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (19%): 'Frn  -    (     1a 45.02.48.03)' vs 'Fondul European de Dezvoltare Regională '</t>
+          <t>duplicate of p8 with different values</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V4_hierarchy</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>49.02</t>
+          <t>61.02.50</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>rând absent, derivat aritmetic din formula părintelui 61.02</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -59237,16 +59208,16 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>61.02.50</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>name mismatch vs nomenclator (35%): '(rând derivat din formula tipărită)' vs 'Alte cheltuieli în domeniul ordinii publ'</t>
         </is>
       </c>
     </row>
@@ -59262,7 +59233,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -59271,14 +59242,14 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>duplicate of p5 with different values</t>
+          <t>duplicate of p8 with different values</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -59287,16 +59258,16 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>85.01</t>
+          <t>61.02.03</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (29%): 'PLA     I S   NT' vs 'Plăţi efectuate în anii precedenţi şi re'</t>
+          <t>duplicate of p9 with different values</t>
         </is>
       </c>
     </row>
@@ -59312,48 +59283,48 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>50.02</t>
+          <t>61.02.03.04</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>duplicate of p6 with different values</t>
+          <t>duplicate of p9 with different values</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>56.02</t>
+          <t>61.02.05</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>rând absent, derivat aritmetic din formula părintelui 50.02</t>
+          <t>duplicate of p9 with different values</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -59362,16 +59333,16 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>56.02</t>
+          <t>63.02</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (36%): '(rând derivat din formula tipărită)' vs 'Transferuri cu caracter general intre di'</t>
+          <t>duplicate of p9 with different values</t>
         </is>
       </c>
     </row>
@@ -59391,12 +59362,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>51.02</t>
+          <t>65.02</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>duplicate of p6 with different values</t>
+          <t>duplicate of p9 with different values</t>
         </is>
       </c>
     </row>
@@ -59412,16 +59383,16 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>51.02.01</t>
+          <t>65.02.03</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>duplicate of p7 with different values</t>
+          <t>duplicate of p11 with different values</t>
         </is>
       </c>
     </row>
@@ -59437,16 +59408,16 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>51.02.01.03</t>
+          <t>65.02.03.01</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>duplicate of p7 with different values</t>
+          <t>duplicate of p11 with different values</t>
         </is>
       </c>
     </row>
@@ -59462,48 +59433,48 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>59.02</t>
+          <t>65.02.03.02</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>duplicate of p8 with different values</t>
+          <t>duplicate of p11 with different values</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>60.02</t>
+          <t>65.02.04</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>rând absent, derivat aritmetic din formula părintelui 59.02</t>
+          <t>duplicate of p11 with different values</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -59512,16 +59483,16 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>60.02</t>
+          <t>65.02.04.01</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (24%): '(rând derivat din formula tipărită)' vs 'Aparare'</t>
+          <t>duplicate of p11 with different values</t>
         </is>
       </c>
     </row>
@@ -59537,48 +59508,48 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>61.02</t>
+          <t>65.02.04.02</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>duplicate of p8 with different values</t>
+          <t>duplicate of p11 with different values</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>61.02.50</t>
+          <t>65.02.04.03</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>rând absent, derivat aritmetic din formula părintelui 61.02</t>
+          <t>duplicate of p11 with different values</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -59587,16 +59558,16 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>61.02.50</t>
+          <t>65.02.13</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (35%): '(rând derivat din formula tipărită)' vs 'Alte cheltuieli în domeniul ordinii publ'</t>
+          <t>duplicate of p11 with different values</t>
         </is>
       </c>
     </row>
@@ -59612,48 +59583,48 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>66.02</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>duplicate of p8 with different values</t>
+          <t>duplicate of p11 with different values</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V4_hierarchy</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>61.02.03</t>
+          <t>66.02.50</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>duplicate of p9 with different values</t>
+          <t>rând absent, derivat aritmetic din formula părintelui 66.02</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -59662,16 +59633,16 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>61.02.03.04</t>
+          <t>66.02.50</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>duplicate of p9 with different values</t>
+          <t>name mismatch vs nomenclator (39%): '(rând derivat din formula tipărită)' vs 'Alte cheltuieli in domeniu sanatatii'</t>
         </is>
       </c>
     </row>
@@ -59687,16 +59658,16 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>61.02.05</t>
+          <t>66.02.08</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>duplicate of p9 with different values</t>
+          <t>duplicate of p12 with different values</t>
         </is>
       </c>
     </row>
@@ -59712,16 +59683,16 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>63.02</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>duplicate of p9 with different values</t>
+          <t>duplicate of p12 with different values</t>
         </is>
       </c>
     </row>
@@ -59737,66 +59708,76 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>65.02</t>
+          <t>51</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>duplicate of p9 with different values</t>
+          <t>duplicate of p13 with different values</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>65.02.03</t>
+          <t>68.02</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>duplicate of p11 with different values</t>
+          <t>68.02 total_2026: parent 7.714.900,00 != sum(children) 47.820.180,00 (5 children)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>65.02.03.01</t>
+          <t>68.02</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>duplicate of p11 with different values</t>
+          <t>68.02 total_2026: parent 7.714.900,00 != sum(children) 12.117.420,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -59812,16 +59793,16 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>65.02.03.02</t>
+          <t>56</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>duplicate of p11 with different values</t>
+          <t>duplicate of p16 with different values</t>
         </is>
       </c>
     </row>
@@ -59837,16 +59818,16 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>65.02.04</t>
+          <t>56.48</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>duplicate of p11 with different values</t>
+          <t>duplicate of p16 with different values</t>
         </is>
       </c>
     </row>
@@ -59862,16 +59843,16 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>65.02.04.01</t>
+          <t>56.48.02</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>duplicate of p11 with different values</t>
+          <t>duplicate of p16 with different values</t>
         </is>
       </c>
     </row>
@@ -59887,16 +59868,16 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>65.02.04.02</t>
+          <t>56.48.03</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>duplicate of p11 with different values</t>
+          <t>duplicate of p16 with different values</t>
         </is>
       </c>
     </row>
@@ -59912,16 +59893,16 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>65.02.04.03</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>duplicate of p11 with different values</t>
+          <t>duplicate of p16 with different values</t>
         </is>
       </c>
     </row>
@@ -59937,16 +59918,16 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>65.02.13</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>duplicate of p11 with different values</t>
+          <t>duplicate of p16 with different values</t>
         </is>
       </c>
     </row>
@@ -59962,48 +59943,48 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>66.02</t>
+          <t>71.01</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>duplicate of p11 with different values</t>
+          <t>duplicate of p16 with different values</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>66.02.50</t>
+          <t>71.01.01</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>rând absent, derivat aritmetic din formula părintelui 66.02</t>
+          <t>duplicate of p16 with different values</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -60012,23 +59993,23 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>66.02.50</t>
+          <t>71.01.30</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (39%): '(rând derivat din formula tipărită)' vs 'Alte cheltuieli in domeniu sanatatii'</t>
+          <t>duplicate of p16 with different values</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -60037,16 +60018,16 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>66.02.08</t>
+          <t>85</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>duplicate of p12 with different values</t>
+          <t>name mismatch vs nomenclator (24%): 'TITLE    I       INT' vs 'Titlul XXII Plăţi efectuate în anii prec'</t>
         </is>
       </c>
     </row>
@@ -60062,16 +60043,16 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>67.02</t>
+          <t>68.02.04</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>duplicate of p12 with different values</t>
+          <t>duplicate of p15 with different values</t>
         </is>
       </c>
     </row>
@@ -60087,28 +60068,28 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>68.02.50</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>duplicate of p13 with different values</t>
+          <t>duplicate of p15 with different values</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B125" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -60116,17 +60097,12 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>68.02</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>68.02.50.50</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>68.02 total_2026: parent 7.714.900,00 != sum(children) 47.820.180,00 (5 children)</t>
+          <t>duplicate of p15 with different values</t>
         </is>
       </c>
     </row>
@@ -60146,7 +60122,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>68.02</t>
+          <t>70.02</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -60156,19 +60132,19 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>68.02 total_2026: parent 7.714.900,00 != sum(children) 12.117.420,00 (2 children)</t>
+          <t>70.02 total_2026: parent 33.584.420,00 != sum(children) 43.492.700,00 (4 children)</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -60176,19 +60152,24 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>70.02</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>duplicate of p16 with different values</t>
+          <t>70.02 total_2026: parent 33.584.420,00 != sum(children) 12.117.420,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -60197,16 +60178,16 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>56.48</t>
+          <t>85</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>duplicate of p16 with different values</t>
+          <t>name mismatch vs nomenclator (22%): 'TITLE       L    NT' vs 'Titlul XXII Plăţi efectuate în anii prec'</t>
         </is>
       </c>
     </row>
@@ -60222,11 +60203,11 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>56.48.02</t>
+          <t>70.02.03</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -60238,32 +60219,32 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V4_hierarchy</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>56.48.03</t>
+          <t>70.02.03.01</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>duplicate of p16 with different values</t>
+          <t>rând absent, derivat aritmetic din formula părintelui 70.02.03</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -60272,16 +60253,16 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>70.02.03.01</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>duplicate of p16 with different values</t>
+          <t>name mismatch vs nomenclator (41%): '(rând derivat din formula tipărită)' vs 'Dezvoltarea sistemului de locuinte'</t>
         </is>
       </c>
     </row>
@@ -60297,11 +60278,11 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>70.02.03.30</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -60322,11 +60303,11 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>71.01</t>
+          <t>70.02.05</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -60338,32 +60319,32 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V4_hierarchy</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>71.01.01</t>
+          <t>70.02.05.02</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>duplicate of p16 with different values</t>
+          <t>rând absent, derivat aritmetic din formula părintelui 70.02.05</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -60372,23 +60353,23 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>71.01.30</t>
+          <t>70.02.05.02</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>duplicate of p16 with different values</t>
+          <t>name mismatch vs nomenclator (32%): '(rând derivat din formula tipărită)' vs 'Amenajari hidrotehnice'</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -60397,16 +60378,16 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>70.02.05.01</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (24%): 'TITLE    I       INT' vs 'Titlul XXII Plăţi efectuate în anii prec'</t>
+          <t>duplicate of p17 with different values</t>
         </is>
       </c>
     </row>
@@ -60422,16 +60403,16 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>68.02.04</t>
+          <t>70.02.06</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>duplicate of p15 with different values</t>
+          <t>duplicate of p17 with different values</t>
         </is>
       </c>
     </row>
@@ -60447,16 +60428,16 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>68.02.50</t>
+          <t>70.02.50</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>duplicate of p15 with different values</t>
+          <t>duplicate of p17 with different values</t>
         </is>
       </c>
     </row>
@@ -60472,83 +60453,73 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>68.02.50.50</t>
+          <t>74.02</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>duplicate of p15 with different values</t>
+          <t>duplicate of p17 with different values</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B140" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>70.02</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>74.02.03</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>70.02 total_2026: parent 33.584.420,00 != sum(children) 43.492.700,00 (4 children)</t>
+          <t>duplicate of p17 with different values</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B141" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>70.02</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>74.02.05</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>70.02 total_2026: parent 33.584.420,00 != sum(children) 12.117.420,00 (2 children)</t>
+          <t>duplicate of p17 with different values</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -60561,12 +60532,12 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>74.02.05.01</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (22%): 'TITLE       L    NT' vs 'Titlul XXII Plăţi efectuate în anii prec'</t>
+          <t>duplicate of p17 with different values</t>
         </is>
       </c>
     </row>
@@ -60586,24 +60557,24 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>70.02.03</t>
+          <t>79.02</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>duplicate of p16 with different values</t>
+          <t>duplicate of p17 with different values</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -60611,24 +60582,24 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>70.02.03.01</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>rând absent, derivat aritmetic din formula părintelui 70.02.03</t>
+          <t>duplicate of p17 with different values</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V4_hierarchy</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -60636,19 +60607,19 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>70.02.03.01</t>
+          <t>80.02.02</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (41%): '(rând derivat din formula tipărită)' vs 'Dezvoltarea sistemului de locuinte'</t>
+          <t>rând absent, derivat aritmetic din formula părintelui 80.02</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -60661,19 +60632,19 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>70.02.03.30</t>
+          <t>80.02.02</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>duplicate of p16 with different values</t>
+          <t>name mismatch vs nomenclator (37%): '(rând derivat din formula tipărită)' vs 'Actiuni generale de munca'</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -60686,24 +60657,24 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>70.02.05</t>
+          <t>80.02.01</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>duplicate of p16 with different values</t>
+          <t>name mismatch vs nomenclator (16%): 'Acet.+0..+.+ 0. 0  0  .30)' vs 'Actiuni generale economice si comerciale'</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -60711,19 +60682,19 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>70.02.05.02</t>
+          <t>80.02.01</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>rând absent, derivat aritmetic din formula părintelui 70.02.05</t>
+          <t>duplicate of p18 with different values</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -60736,19 +60707,19 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>70.02.05.02</t>
+          <t>80.02.01.30</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (32%): '(rând derivat din formula tipărită)' vs 'Amenajari hidrotehnice'</t>
+          <t>duplicate of p18 with different values</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -60761,12 +60732,12 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>70.02.05.01</t>
+          <t>84.02</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>duplicate of p17 with different values</t>
+          <t>name mismatch vs nomenclator (12%): 'r1a..+..+..+. 0. 50)' vs 'Transporturi'</t>
         </is>
       </c>
     </row>
@@ -60786,12 +60757,12 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>70.02.06</t>
+          <t>84.02</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>duplicate of p17 with different values</t>
+          <t>duplicate of p18 with different values</t>
         </is>
       </c>
     </row>
@@ -60807,16 +60778,16 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>70.02.50</t>
+          <t>84.02.03</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>duplicate of p17 with different values</t>
+          <t>duplicate of p19 with different values</t>
         </is>
       </c>
     </row>
@@ -60832,16 +60803,16 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>74.02</t>
+          <t>84.02.03.01</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>duplicate of p17 with different values</t>
+          <t>duplicate of p19 with different values</t>
         </is>
       </c>
     </row>
@@ -60857,364 +60828,14 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>74.02.03</t>
+          <t>84.02.03.02</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
-        <is>
-          <t>duplicate of p17 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C155" t="n">
-        <v>39</v>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>74.02.05</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>duplicate of p17 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C156" t="n">
-        <v>39</v>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>74.02.05.01</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>duplicate of p17 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C157" t="n">
-        <v>39</v>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>79.02</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>duplicate of p17 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C158" t="n">
-        <v>39</v>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>80.02</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>duplicate of p17 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>info</t>
-        </is>
-      </c>
-      <c r="C159" t="n">
-        <v>39</v>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>80.02.02</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>rând absent, derivat aritmetic din formula părintelui 80.02</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C160" t="n">
-        <v>39</v>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>80.02.02</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (37%): '(rând derivat din formula tipărită)' vs 'Actiuni generale de munca'</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C161" t="n">
-        <v>39</v>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>80.02.01</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (16%): 'Acet.+0..+.+ 0. 0  0  .30)' vs 'Actiuni generale economice si comerciale'</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C162" t="n">
-        <v>39</v>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>80.02.01</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>duplicate of p18 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C163" t="n">
-        <v>39</v>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>80.02.01.30</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>duplicate of p18 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C164" t="n">
-        <v>39</v>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>84.02</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (12%): 'r1a..+..+..+. 0. 50)' vs 'Transporturi'</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C165" t="n">
-        <v>39</v>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>84.02</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>duplicate of p18 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C166" t="n">
-        <v>40</v>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>84.02.03</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>duplicate of p19 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C167" t="n">
-        <v>40</v>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>84.02.03.01</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>duplicate of p19 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C168" t="n">
-        <v>40</v>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>84.02.03.02</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
         <is>
           <t>duplicate of p19 with different values</t>
         </is>
@@ -61231,7 +60852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -61253,7 +60874,7 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Documente</t>
+          <t>Schema calitate</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -61263,72 +60884,230 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>Linii de date</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1676</v>
+          <t>Metrica de calitate</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>observed_strict_line_rate</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Linii fara probleme</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1549</v>
+          <t>Recall masurat</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>nu</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>% curat</t>
+          <t>Documente</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>92.40000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Erori</t>
+          <t>Linii de date</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>44</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Avertismente</t>
+          <t>Linii strict verificate</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>103</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Modele LLM folosite</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>gemini-3.6-flash</t>
-        </is>
+          <t>% linii strict verificate</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>92.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
+          <t>Celule numerice</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1671</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Celule numerice strict verificate</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1544</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>% celule numerice strict verificate</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>92.40000000000001</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Pagini asteptate</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Pagini selectate</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Pagini procesate</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>PDF complet</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Linii fara probleme</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1545</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>% curat</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>92.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Erori</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Avertismente</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Informatii</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Schema publicare</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Bundle conversie</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>b9fd50c8e10f4115e44636bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>SHA-256 PDF sursa</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2edd0eb570404b0f01b4ccf8fe8149aa797cbed2d361276859f7eaa0dd11a1e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
           <t>— Anexa (de la pagina 1)</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>local, pag. 1-40, 1743 linii</t>
         </is>
